--- a/forms/trg/Formulir_TRG_fderg.xlsx
+++ b/forms/trg/Formulir_TRG_fderg.xlsx
@@ -940,7 +940,11 @@
           <t>Faisal Mahmuddin</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1235,7 +1239,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1268,7 +1272,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1297,7 +1301,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
